--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0E99C8-1BBE-443F-8014-F9E6E180C0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F2961E-2DCD-4BE0-9379-2CD4E11FCE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>Felt tired in night</t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
   </si>
 </sst>
 </file>
@@ -1233,334 +1236,694 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B11" s="14">
+        <v>400</v>
+      </c>
+      <c r="C11" s="14">
+        <v>67</v>
+      </c>
+      <c r="D11" s="14">
+        <v>200</v>
+      </c>
+      <c r="E11" s="14">
+        <v>80</v>
+      </c>
+      <c r="F11" s="14">
+        <v>180</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>10</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>937</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>503</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46270</v>
+      </c>
+      <c r="B12" s="14">
+        <v>367</v>
+      </c>
+      <c r="C12" s="14">
+        <v>54</v>
+      </c>
+      <c r="D12" s="14">
+        <v>877</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>37</v>
+      </c>
+      <c r="G12" s="14">
+        <v>4</v>
+      </c>
+      <c r="H12" s="14">
+        <v>13</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1438</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46271</v>
+      </c>
+      <c r="B13" s="14">
+        <v>456</v>
+      </c>
+      <c r="C13" s="14">
+        <v>45</v>
+      </c>
+      <c r="D13" s="14">
+        <v>400</v>
+      </c>
+      <c r="E13" s="14">
+        <v>98</v>
+      </c>
+      <c r="F13" s="14">
+        <v>342</v>
+      </c>
+      <c r="G13" s="14">
+        <v>3</v>
+      </c>
+      <c r="H13" s="14">
+        <v>90</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>1431</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>9</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13">
+        <v>46272</v>
+      </c>
+      <c r="B14" s="14">
+        <v>433</v>
+      </c>
+      <c r="C14" s="14">
+        <v>44</v>
+      </c>
+      <c r="D14" s="14">
+        <v>566</v>
+      </c>
+      <c r="E14" s="14">
+        <v>90</v>
+      </c>
+      <c r="F14" s="14">
+        <v>234</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
+        <v>70</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>1437</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>3</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46273</v>
+      </c>
+      <c r="B15" s="14">
+        <v>567</v>
+      </c>
+      <c r="C15" s="14">
+        <v>34</v>
+      </c>
+      <c r="D15" s="14">
+        <v>433</v>
+      </c>
+      <c r="E15" s="14">
+        <v>76</v>
+      </c>
+      <c r="F15" s="14">
+        <v>250</v>
+      </c>
+      <c r="G15" s="14">
+        <v>5</v>
+      </c>
+      <c r="H15" s="14">
+        <v>75</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>1435</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>5</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46274</v>
+      </c>
+      <c r="B16" s="14">
+        <v>544</v>
+      </c>
+      <c r="C16" s="14">
+        <v>43</v>
+      </c>
+      <c r="D16" s="14">
+        <v>334</v>
+      </c>
+      <c r="E16" s="14">
+        <v>78</v>
+      </c>
+      <c r="F16" s="14">
+        <v>300</v>
+      </c>
+      <c r="G16" s="14">
+        <v>4</v>
+      </c>
+      <c r="H16" s="14">
+        <v>140</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>1439</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46275</v>
+      </c>
+      <c r="B17" s="14">
+        <v>456</v>
+      </c>
+      <c r="C17" s="14">
+        <v>67</v>
+      </c>
+      <c r="D17" s="14">
+        <v>321</v>
+      </c>
+      <c r="E17" s="14">
+        <v>98</v>
+      </c>
+      <c r="F17" s="14">
+        <v>322</v>
+      </c>
+      <c r="G17" s="14">
+        <v>6</v>
+      </c>
+      <c r="H17" s="14">
+        <v>170</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>1434</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>6</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46276</v>
+      </c>
+      <c r="B18" s="14">
+        <v>432</v>
+      </c>
+      <c r="C18" s="14">
+        <v>54</v>
+      </c>
+      <c r="D18" s="14">
+        <v>334</v>
+      </c>
+      <c r="E18" s="14">
+        <v>78</v>
+      </c>
+      <c r="F18" s="14">
+        <v>344</v>
+      </c>
+      <c r="G18" s="14">
+        <v>4</v>
+      </c>
+      <c r="H18" s="14">
+        <v>190</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>1432</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>8</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46277</v>
+      </c>
+      <c r="B19" s="14">
+        <v>345</v>
+      </c>
+      <c r="C19" s="14">
+        <v>67</v>
+      </c>
+      <c r="D19" s="14">
+        <v>433</v>
+      </c>
+      <c r="E19" s="14">
+        <v>340</v>
+      </c>
+      <c r="F19" s="14">
+        <v>159</v>
+      </c>
+      <c r="G19" s="14">
+        <v>6</v>
+      </c>
+      <c r="H19" s="14">
+        <v>90</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>1434</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>6</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="A20" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B20" s="14">
+        <v>332</v>
+      </c>
+      <c r="C20" s="14">
+        <v>44</v>
+      </c>
+      <c r="D20" s="14">
+        <v>345</v>
+      </c>
+      <c r="E20" s="14">
+        <v>567</v>
+      </c>
+      <c r="F20" s="14">
+        <v>90</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>1438</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>2</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B21" s="14">
+        <v>456</v>
+      </c>
+      <c r="C21" s="14">
+        <v>67</v>
+      </c>
+      <c r="D21" s="14">
+        <v>433</v>
+      </c>
+      <c r="E21" s="14">
+        <v>56</v>
+      </c>
+      <c r="F21" s="14">
+        <v>340</v>
+      </c>
+      <c r="G21" s="14">
+        <v>7</v>
+      </c>
+      <c r="H21" s="14">
+        <v>80</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>1432</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>8</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
+      <c r="A22" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B22" s="14">
+        <v>324</v>
+      </c>
+      <c r="C22" s="14">
+        <v>44</v>
+      </c>
+      <c r="D22" s="14">
+        <v>234</v>
+      </c>
+      <c r="E22" s="14">
+        <v>654</v>
+      </c>
+      <c r="F22" s="14">
+        <v>100</v>
+      </c>
+      <c r="G22" s="14">
+        <v>7</v>
+      </c>
+      <c r="H22" s="14">
+        <v>80</v>
+      </c>
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
+        <v>1436</v>
+      </c>
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
+        <v>4</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
+      <c r="A23" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B23" s="14">
+        <v>456</v>
+      </c>
+      <c r="C23" s="14">
+        <v>67</v>
+      </c>
+      <c r="D23" s="14">
+        <v>322</v>
+      </c>
+      <c r="E23" s="14">
+        <v>145</v>
+      </c>
+      <c r="F23" s="14">
+        <v>322</v>
+      </c>
+      <c r="G23" s="14">
+        <v>7</v>
+      </c>
+      <c r="H23" s="14">
+        <v>120</v>
+      </c>
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
+        <v>1432</v>
+      </c>
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
+        <v>8</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N23" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
+      <c r="A24" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B24" s="14">
+        <v>432</v>
+      </c>
+      <c r="C24" s="14">
+        <v>54</v>
+      </c>
+      <c r="D24" s="14">
+        <v>344</v>
+      </c>
+      <c r="E24" s="14">
+        <v>245</v>
+      </c>
+      <c r="F24" s="14">
+        <v>322</v>
+      </c>
+      <c r="G24" s="14">
+        <v>8</v>
+      </c>
+      <c r="H24" s="14">
+        <v>40</v>
+      </c>
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
+        <v>1437</v>
+      </c>
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
+        <v>3</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
+      <c r="A25" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B25" s="14">
+        <v>456</v>
+      </c>
+      <c r="C25" s="14">
+        <v>67</v>
+      </c>
+      <c r="D25" s="14">
+        <v>322</v>
+      </c>
+      <c r="E25" s="14">
+        <v>345</v>
+      </c>
+      <c r="F25" s="14">
+        <v>232</v>
+      </c>
+      <c r="G25" s="14">
+        <v>8</v>
+      </c>
+      <c r="H25" s="14">
+        <v>10</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
+        <v>1432</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>8</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A26" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F2961E-2DCD-4BE0-9379-2CD4E11FCE95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81A0CBD-EBA1-4C0E-8D89-8212B309A69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="66">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,12 @@
   </si>
   <si>
     <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>Felt tired in night due to CA missed</t>
   </si>
 </sst>
 </file>
@@ -1925,27 +1931,51 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
+    <row r="26" spans="1:14" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A26" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B26" s="14">
+        <v>450</v>
+      </c>
+      <c r="C26" s="14">
+        <v>66</v>
+      </c>
+      <c r="D26" s="14">
+        <v>329</v>
+      </c>
+      <c r="E26" s="14">
+        <v>340</v>
+      </c>
+      <c r="F26" s="14">
+        <v>239</v>
+      </c>
+      <c r="G26" s="14">
+        <v>5</v>
+      </c>
+      <c r="H26" s="14">
+        <v>12</v>
+      </c>
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
+        <v>1436</v>
+      </c>
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+        <v>4</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A27" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B81A0CBD-EBA1-4C0E-8D89-8212B309A69A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988CAA36-81D4-4270-8063-181AD7902B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>Felt tired in night due to CA missed</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>SUNDAY</t>
   </si>
 </sst>
 </file>
@@ -1978,26 +1984,50 @@
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A27" s="13"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15" t="str">
+      <c r="A27" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B27" s="14">
+        <v>445</v>
+      </c>
+      <c r="C27" s="14">
+        <v>56</v>
+      </c>
+      <c r="D27" s="14">
+        <v>320</v>
+      </c>
+      <c r="E27" s="14">
+        <v>330</v>
+      </c>
+      <c r="F27" s="14">
+        <v>250</v>
+      </c>
+      <c r="G27" s="14">
+        <v>7</v>
+      </c>
+      <c r="H27" s="14">
+        <v>29</v>
+      </c>
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="15" t="str">
+        <v>1430</v>
+      </c>
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" s="17"/>
+        <v>10</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L27" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M27" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N27" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A28" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988CAA36-81D4-4270-8063-181AD7902B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABE2376-B9A4-4DE3-AD7D-C11AD982D00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,9 @@
   </si>
   <si>
     <t>SUNDAY</t>
+  </si>
+  <si>
+    <t>felt bore</t>
   </si>
 </sst>
 </file>
@@ -2030,26 +2033,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A28" s="13"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15" t="str">
+      <c r="A28" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B28" s="14">
+        <v>400</v>
+      </c>
+      <c r="C28" s="14">
+        <v>62</v>
+      </c>
+      <c r="D28" s="14">
+        <v>300</v>
+      </c>
+      <c r="E28" s="14">
+        <v>300</v>
+      </c>
+      <c r="F28" s="14">
+        <v>200</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>45</v>
+      </c>
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="15" t="str">
+        <v>1307</v>
+      </c>
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="17"/>
+        <v>133</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N28" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A29" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ABE2376-B9A4-4DE3-AD7D-C11AD982D00D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FB7155-D16B-4DD2-BAAC-C5F61357A722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>felt bore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feel happy </t>
   </si>
 </sst>
 </file>
@@ -2079,26 +2082,50 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A29" s="13"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15" t="str">
+      <c r="A29" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B29" s="14">
+        <v>409</v>
+      </c>
+      <c r="C29" s="14">
+        <v>70</v>
+      </c>
+      <c r="D29" s="14">
+        <v>245</v>
+      </c>
+      <c r="E29" s="14">
+        <v>321</v>
+      </c>
+      <c r="F29" s="14">
+        <v>322</v>
+      </c>
+      <c r="G29" s="14">
+        <v>5</v>
+      </c>
+      <c r="H29" s="14">
+        <v>50</v>
+      </c>
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="15" t="str">
+        <v>1417</v>
+      </c>
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" s="16"/>
-      <c r="N29" s="17"/>
+        <v>23</v>
+      </c>
+      <c r="K29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L29" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M29" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N29" s="17" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A30" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24FB7155-D16B-4DD2-BAAC-C5F61357A722}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2648593B-675C-4A07-A809-1316DAD1A5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t xml:space="preserve">Feel happy </t>
+  </si>
+  <si>
+    <t>felt tired</t>
   </si>
 </sst>
 </file>
@@ -2128,26 +2131,50 @@
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A30" s="13"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15" t="str">
+      <c r="A30" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B30" s="14">
+        <v>333</v>
+      </c>
+      <c r="C30" s="14">
+        <v>50</v>
+      </c>
+      <c r="D30" s="14">
+        <v>300</v>
+      </c>
+      <c r="E30" s="14">
+        <v>140</v>
+      </c>
+      <c r="F30" s="14">
+        <v>400</v>
+      </c>
+      <c r="G30" s="14">
+        <v>6</v>
+      </c>
+      <c r="H30" s="14">
+        <v>200</v>
+      </c>
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="15" t="str">
+        <v>1423</v>
+      </c>
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" s="17"/>
+        <v>17</v>
+      </c>
+      <c r="K30" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L30" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M30" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N30" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A31" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2648593B-675C-4A07-A809-1316DAD1A5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DDF8CD-04D8-4368-B6A5-894BA4A14E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>felt tired</t>
+  </si>
+  <si>
+    <t>Feel better today</t>
   </si>
 </sst>
 </file>
@@ -2177,26 +2180,50 @@
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A31" s="13"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15" t="str">
+      <c r="A31" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B31" s="14">
+        <v>300</v>
+      </c>
+      <c r="C31" s="14">
+        <v>30</v>
+      </c>
+      <c r="D31" s="14">
+        <v>320</v>
+      </c>
+      <c r="E31" s="14">
+        <v>100</v>
+      </c>
+      <c r="F31" s="14">
+        <v>450</v>
+      </c>
+      <c r="G31" s="14">
+        <v>5</v>
+      </c>
+      <c r="H31" s="14">
+        <v>150</v>
+      </c>
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L31" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N31" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A32" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0DDF8CD-04D8-4368-B6A5-894BA4A14E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED8488B-44BB-4B23-9856-2712EBD99D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Feel better today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Due to examnation </t>
   </si>
 </sst>
 </file>
@@ -2226,26 +2229,50 @@
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A32" s="13"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15" t="str">
+      <c r="A32" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B32" s="14">
+        <v>240</v>
+      </c>
+      <c r="C32" s="14">
+        <v>45</v>
+      </c>
+      <c r="D32" s="14">
+        <v>400</v>
+      </c>
+      <c r="E32" s="14">
+        <v>120</v>
+      </c>
+      <c r="F32" s="14">
+        <v>367</v>
+      </c>
+      <c r="G32" s="14">
+        <v>6</v>
+      </c>
+      <c r="H32" s="14">
+        <v>200</v>
+      </c>
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="15" t="str">
+        <v>1372</v>
+      </c>
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" s="16"/>
-      <c r="N32" s="17"/>
+        <v>68</v>
+      </c>
+      <c r="K32" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L32" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M32" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N32" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A33" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED8488B-44BB-4B23-9856-2712EBD99D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3C9E10-9741-491E-B701-4E43534D795C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t xml:space="preserve">Due to examnation </t>
+  </si>
+  <si>
+    <t>Saturday</t>
   </si>
 </sst>
 </file>
@@ -2275,26 +2278,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A33" s="13"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B33" s="14">
+        <v>200</v>
+      </c>
+      <c r="C33" s="14">
+        <v>40</v>
+      </c>
+      <c r="D33" s="14">
+        <v>500</v>
+      </c>
+      <c r="E33" s="14">
+        <v>140</v>
+      </c>
+      <c r="F33" s="14">
+        <v>200</v>
+      </c>
+      <c r="G33" s="14">
+        <v>8</v>
+      </c>
+      <c r="H33" s="14">
+        <v>300</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A34" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF3C9E10-9741-491E-B701-4E43534D795C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C034C2E9-4D04-4321-89CC-FAB1587522E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -257,6 +257,9 @@
   </si>
   <si>
     <t>Saturday</t>
+  </si>
+  <si>
+    <t>Protest At college</t>
   </si>
 </sst>
 </file>
@@ -2324,26 +2327,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B34" s="14">
+        <v>400</v>
+      </c>
+      <c r="C34" s="14">
+        <v>20</v>
+      </c>
+      <c r="D34" s="14">
+        <v>100</v>
+      </c>
+      <c r="E34" s="14">
+        <v>50</v>
+      </c>
+      <c r="F34" s="14">
+        <v>200</v>
+      </c>
+      <c r="G34" s="14">
+        <v>3</v>
+      </c>
+      <c r="H34" s="14">
+        <v>500</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>170</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A35" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C034C2E9-4D04-4321-89CC-FAB1587522E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE86EC8-803D-4904-9C5B-044521C6A001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Protest At college</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fell better </t>
   </si>
 </sst>
 </file>
@@ -2373,26 +2376,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B35" s="14">
+        <v>300</v>
+      </c>
+      <c r="C35" s="14">
+        <v>20</v>
+      </c>
+      <c r="D35" s="14">
+        <v>299</v>
+      </c>
+      <c r="E35" s="14">
+        <v>23</v>
+      </c>
+      <c r="F35" s="14">
+        <v>400</v>
+      </c>
+      <c r="G35" s="14">
+        <v>4</v>
+      </c>
+      <c r="H35" s="14">
+        <v>350</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1392</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>48</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A36" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE86EC8-803D-4904-9C5B-044521C6A001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7131C607-CD6E-4DB8-8738-5035DF597684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2422,26 +2422,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B36" s="14">
+        <v>249</v>
+      </c>
+      <c r="C36" s="14">
+        <v>23</v>
+      </c>
+      <c r="D36" s="14">
+        <v>444</v>
+      </c>
+      <c r="E36" s="14">
+        <v>234</v>
+      </c>
+      <c r="F36" s="14">
+        <v>432</v>
+      </c>
+      <c r="G36" s="14">
+        <v>4</v>
+      </c>
+      <c r="H36" s="14">
+        <v>20</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1402</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>38</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A37" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7131C607-CD6E-4DB8-8738-5035DF597684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C390F8-D8B6-4F3C-9D6B-CE5AC014FC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2468,26 +2468,46 @@
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A37" s="13"/>
+      <c r="A37" s="13">
+        <v>46295</v>
+      </c>
       <c r="B37" s="14"/>
       <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+      <c r="D37" s="14">
+        <v>340</v>
+      </c>
+      <c r="E37" s="14">
+        <v>394</v>
+      </c>
+      <c r="F37" s="14">
+        <v>334</v>
+      </c>
+      <c r="G37" s="14">
+        <v>3</v>
+      </c>
+      <c r="H37" s="14">
+        <v>43</v>
+      </c>
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1111</v>
+      </c>
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
+        <v>329</v>
+      </c>
+      <c r="K37" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M37" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N37" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A38" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65C390F8-D8B6-4F3C-9D6B-CE5AC014FC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13D81A2-7408-419A-B4CA-DA3D7447D80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2471,8 +2471,12 @@
       <c r="A37" s="13">
         <v>46295</v>
       </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
+      <c r="B37" s="14">
+        <v>299</v>
+      </c>
+      <c r="C37" s="14">
+        <v>20</v>
+      </c>
       <c r="D37" s="14">
         <v>340</v>
       </c>
@@ -2490,14 +2494,14 @@
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>1111</v>
+        <v>1430</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>329</v>
+        <v>10</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="L37" s="16" t="s">
         <v>50</v>
@@ -2510,21 +2514,37 @@
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
+      <c r="A38" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B38" s="14">
+        <v>300</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>120</v>
+      </c>
+      <c r="E38" s="14">
+        <v>100</v>
+      </c>
+      <c r="F38" s="14">
+        <v>200</v>
+      </c>
+      <c r="G38" s="14">
+        <v>3</v>
+      </c>
+      <c r="H38" s="14">
+        <v>500</v>
+      </c>
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
+        <v>1250</v>
+      </c>
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v/>
+        <v>190</v>
       </c>
       <c r="K38" s="16"/>
       <c r="L38" s="16"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D13D81A2-7408-419A-B4CA-DA3D7447D80A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5003B064-E67D-4C99-8D87-AC0F57ADC8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2546,32 +2546,64 @@
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
+      <c r="K38" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L38" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M38" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N38" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
+      <c r="A39" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B39" s="14">
+        <v>400</v>
+      </c>
+      <c r="C39" s="14">
+        <v>45</v>
+      </c>
+      <c r="D39" s="14">
+        <v>200</v>
+      </c>
+      <c r="E39" s="14">
+        <v>50</v>
+      </c>
+      <c r="F39" s="14">
+        <v>299</v>
+      </c>
+      <c r="G39" s="14">
+        <v>5</v>
+      </c>
+      <c r="H39" s="14">
+        <v>400</v>
+      </c>
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
+        <v>1394</v>
+      </c>
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
+        <v>46</v>
+      </c>
+      <c r="K39" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L39" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M39" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N39" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A40" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5003B064-E67D-4C99-8D87-AC0F57ADC8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCB9B18-FB45-4663-B114-83EA975BCCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fell better </t>
+  </si>
+  <si>
+    <t>At home</t>
   </si>
 </sst>
 </file>
@@ -2606,26 +2609,50 @@
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
+      <c r="A40" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B40" s="14">
+        <v>450</v>
+      </c>
+      <c r="C40" s="14">
+        <v>30</v>
+      </c>
+      <c r="D40" s="14">
+        <v>150</v>
+      </c>
+      <c r="E40" s="14">
+        <v>100</v>
+      </c>
+      <c r="F40" s="14">
+        <v>100</v>
+      </c>
+      <c r="G40" s="14">
+        <v>2</v>
+      </c>
+      <c r="H40" s="14">
+        <v>550</v>
+      </c>
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K40" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L40" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N40" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A41" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FCB9B18-FB45-4663-B114-83EA975BCCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C555B870-DA64-42F5-B15A-F871EF871AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2655,26 +2655,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B41" s="14">
+        <v>400</v>
+      </c>
+      <c r="C41" s="14">
+        <v>23</v>
+      </c>
+      <c r="D41" s="14">
+        <v>344</v>
+      </c>
+      <c r="E41" s="14">
+        <v>213</v>
+      </c>
+      <c r="F41" s="14">
+        <v>324</v>
+      </c>
+      <c r="G41" s="14">
+        <v>3</v>
+      </c>
+      <c r="H41" s="14">
+        <v>42</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>1346</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>94</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A42" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C555B870-DA64-42F5-B15A-F871EF871AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF15820-C6FD-4289-A007-63473B06ECBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2701,26 +2701,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="13">
+        <v>46300</v>
+      </c>
+      <c r="B42" s="14">
+        <v>400</v>
+      </c>
+      <c r="C42" s="14">
+        <v>23</v>
+      </c>
+      <c r="D42" s="14">
+        <v>345</v>
+      </c>
+      <c r="E42" s="14">
+        <v>345</v>
+      </c>
+      <c r="F42" s="14">
+        <v>34</v>
+      </c>
+      <c r="G42" s="14">
+        <v>5</v>
+      </c>
+      <c r="H42" s="14">
+        <v>64</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1211</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>229</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A43" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF15820-C6FD-4289-A007-63473B06ECBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC74A71-7AC9-415F-970B-BA48352462AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,9 @@
   </si>
   <si>
     <t>At home</t>
+  </si>
+  <si>
+    <t>Feel normal toady</t>
   </si>
 </sst>
 </file>
@@ -2747,26 +2750,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="13">
+        <v>46301</v>
+      </c>
+      <c r="B43" s="14">
+        <v>390</v>
+      </c>
+      <c r="C43" s="14">
+        <v>13</v>
+      </c>
+      <c r="D43" s="14">
+        <v>233</v>
+      </c>
+      <c r="E43" s="14">
+        <v>234</v>
+      </c>
+      <c r="F43" s="14">
+        <v>31</v>
+      </c>
+      <c r="G43" s="14">
+        <v>8</v>
+      </c>
+      <c r="H43" s="14">
+        <v>23</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>924</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>516</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A44" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BC74A71-7AC9-415F-970B-BA48352462AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A0F25E-7911-4A34-987F-EE93BD1CA32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -269,6 +269,9 @@
   </si>
   <si>
     <t>Feel normal toady</t>
+  </si>
+  <si>
+    <t>`12</t>
   </si>
 </sst>
 </file>
@@ -2796,26 +2799,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="13">
+        <v>46302</v>
+      </c>
+      <c r="B44" s="14">
+        <v>300</v>
+      </c>
+      <c r="C44" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" s="14">
+        <v>233</v>
+      </c>
+      <c r="E44" s="14">
+        <v>324</v>
+      </c>
+      <c r="F44" s="14">
+        <v>45</v>
+      </c>
+      <c r="G44" s="14">
+        <v>7</v>
+      </c>
+      <c r="H44" s="14">
+        <v>500</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1402</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>38</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A45" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A0F25E-7911-4A34-987F-EE93BD1CA32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573DD1CA-22D6-4515-A992-ED614B26CF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2845,26 +2845,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46303</v>
+      </c>
+      <c r="B45" s="14">
+        <v>333</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>400</v>
+      </c>
+      <c r="E45" s="14">
+        <v>54</v>
+      </c>
+      <c r="F45" s="14">
+        <v>120</v>
+      </c>
+      <c r="G45" s="14">
+        <v>3</v>
+      </c>
+      <c r="H45" s="14">
+        <v>199</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1136</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>304</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A46" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573DD1CA-22D6-4515-A992-ED614B26CF0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A86627-9B83-42DC-93D4-188C4F065D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-83" yWindow="0" windowWidth="12060" windowHeight="13583" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2891,26 +2891,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46304</v>
+      </c>
+      <c r="B46" s="14">
+        <v>400</v>
+      </c>
+      <c r="C46" s="14">
+        <v>34</v>
+      </c>
+      <c r="D46" s="14">
+        <v>432</v>
+      </c>
+      <c r="E46" s="14">
+        <v>45</v>
+      </c>
+      <c r="F46" s="14">
+        <v>345</v>
+      </c>
+      <c r="G46" s="14">
+        <v>3</v>
+      </c>
+      <c r="H46" s="14">
+        <v>150</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1406</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A47" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49A86627-9B83-42DC-93D4-188C4F065D72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E6110D-5069-4729-B095-97F497189E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="12060" windowHeight="13583" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2937,26 +2937,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46305</v>
+      </c>
+      <c r="B47" s="14">
+        <v>300</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>345</v>
+      </c>
+      <c r="E47" s="14">
+        <v>34</v>
+      </c>
+      <c r="F47" s="14">
+        <v>230</v>
+      </c>
+      <c r="G47" s="14">
+        <v>4</v>
+      </c>
+      <c r="H47" s="14">
+        <v>200</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>1109</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>331</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A48" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E6110D-5069-4729-B095-97F497189E0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C5E53F-0E7F-44FF-B4C5-FFA0CAFAB423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="80">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,9 @@
   </si>
   <si>
     <t>`12</t>
+  </si>
+  <si>
+    <t>fell happy</t>
   </si>
 </sst>
 </file>
@@ -2983,26 +2986,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46306</v>
+      </c>
+      <c r="B48" s="14">
+        <v>340</v>
+      </c>
+      <c r="C48" s="14">
+        <v>10</v>
+      </c>
+      <c r="D48" s="14">
+        <v>400</v>
+      </c>
+      <c r="E48" s="14">
+        <v>40</v>
+      </c>
+      <c r="F48" s="14">
+        <v>200</v>
+      </c>
+      <c r="G48" s="14">
+        <v>6</v>
+      </c>
+      <c r="H48" s="14">
+        <v>400</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>1390</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>50</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9C5E53F-0E7F-44FF-B4C5-FFA0CAFAB423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98863C6-2F47-444F-B552-4531974BC0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -275,6 +275,9 @@
   </si>
   <si>
     <t>fell happy</t>
+  </si>
+  <si>
+    <t>Exam time</t>
   </si>
 </sst>
 </file>
@@ -3032,26 +3035,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B49" s="14">
+        <v>200</v>
+      </c>
+      <c r="C49" s="14">
+        <v>20</v>
+      </c>
+      <c r="D49" s="14">
+        <v>400</v>
+      </c>
+      <c r="E49" s="14">
+        <v>39</v>
+      </c>
+      <c r="F49" s="14">
+        <v>450</v>
+      </c>
+      <c r="G49" s="14">
+        <v>4</v>
+      </c>
+      <c r="H49" s="14">
+        <v>100</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>1209</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>231</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A50" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98863C6-2F47-444F-B552-4531974BC0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFC6347-CD6A-4066-8682-7497CE7650FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3081,26 +3081,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B50" s="14">
+        <v>200</v>
+      </c>
+      <c r="C50" s="14">
+        <v>23</v>
+      </c>
+      <c r="D50" s="14">
+        <v>342</v>
+      </c>
+      <c r="E50" s="14">
+        <v>34</v>
+      </c>
+      <c r="F50" s="14">
+        <v>234</v>
+      </c>
+      <c r="G50" s="14">
+        <v>2</v>
+      </c>
+      <c r="H50" s="14">
+        <v>345</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1178</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>262</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A51" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFC6347-CD6A-4066-8682-7497CE7650FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0CF13C-2C2D-4E33-9AB3-B822326840F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3127,26 +3127,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B51" s="14">
+        <v>300</v>
+      </c>
+      <c r="C51" s="14">
+        <v>23</v>
+      </c>
+      <c r="D51" s="14">
+        <v>321</v>
+      </c>
+      <c r="E51" s="14">
+        <v>343</v>
+      </c>
+      <c r="F51" s="14">
+        <v>34</v>
+      </c>
+      <c r="G51" s="14">
+        <v>4</v>
+      </c>
+      <c r="H51" s="14">
+        <v>200</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1221</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>219</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A52" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E0CF13C-2C2D-4E33-9AB3-B822326840F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4BB3C9-205C-4B13-93E3-0F73D36A65F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3173,26 +3173,46 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A52" s="13"/>
+      <c r="A52" s="13">
+        <v>46310</v>
+      </c>
       <c r="B52" s="14"/>
       <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="D52" s="14">
+        <v>200</v>
+      </c>
+      <c r="E52" s="14">
+        <v>234</v>
+      </c>
+      <c r="F52" s="14">
+        <v>32</v>
+      </c>
+      <c r="G52" s="14">
+        <v>3</v>
+      </c>
+      <c r="H52" s="14">
+        <v>432</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>898</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>542</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A53" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4BB3C9-205C-4B13-93E3-0F73D36A65F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D904B9BB-C641-4E78-92D7-56692C5F024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3176,8 +3176,12 @@
       <c r="A52" s="13">
         <v>46310</v>
       </c>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
+      <c r="B52" s="14">
+        <v>300</v>
+      </c>
+      <c r="C52" s="14">
+        <v>200</v>
+      </c>
       <c r="D52" s="14">
         <v>200</v>
       </c>
@@ -3195,11 +3199,11 @@
       </c>
       <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v>898</v>
+        <v>1398</v>
       </c>
       <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v>542</v>
+        <v>42</v>
       </c>
       <c r="K52" s="16" t="s">
         <v>49</v>
@@ -3215,26 +3219,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B53" s="14">
+        <v>200</v>
+      </c>
+      <c r="C53" s="14">
+        <v>200</v>
+      </c>
+      <c r="D53" s="14">
+        <v>400</v>
+      </c>
+      <c r="E53" s="14">
+        <v>20</v>
+      </c>
+      <c r="F53" s="14">
+        <v>200</v>
+      </c>
+      <c r="G53" s="14">
+        <v>4</v>
+      </c>
+      <c r="H53" s="14">
+        <v>360</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1380</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A54" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D904B9BB-C641-4E78-92D7-56692C5F024E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D4E640-2299-4FDE-96B2-F3DD57CB8336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3265,26 +3265,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="13">
+        <v>46312</v>
+      </c>
+      <c r="B54" s="14">
+        <v>250</v>
+      </c>
+      <c r="C54" s="14">
+        <v>29</v>
+      </c>
+      <c r="D54" s="14">
+        <v>450</v>
+      </c>
+      <c r="E54" s="14">
+        <v>45</v>
+      </c>
+      <c r="F54" s="14">
+        <v>250</v>
+      </c>
+      <c r="G54" s="14">
+        <v>5</v>
+      </c>
+      <c r="H54" s="14">
+        <v>250</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1274</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>166</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A55" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D4E640-2299-4FDE-96B2-F3DD57CB8336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D6A78E-6B06-455E-8AB5-B25CDC8E2197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -278,6 +278,9 @@
   </si>
   <si>
     <t>Exam time</t>
+  </si>
+  <si>
+    <t>Feel good todayS</t>
   </si>
 </sst>
 </file>
@@ -3311,26 +3314,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="13">
+        <v>46313</v>
+      </c>
+      <c r="B55" s="14">
+        <v>200</v>
+      </c>
+      <c r="C55" s="14">
+        <v>30</v>
+      </c>
+      <c r="D55" s="14">
+        <v>400</v>
+      </c>
+      <c r="E55" s="14">
+        <v>30</v>
+      </c>
+      <c r="F55" s="14">
+        <v>200</v>
+      </c>
+      <c r="G55" s="14">
+        <v>4</v>
+      </c>
+      <c r="H55" s="14">
+        <v>300</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>280</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A56" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D6A78E-6B06-455E-8AB5-B25CDC8E2197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12968C3C-C029-4765-BCB7-65814F8786FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -280,7 +280,7 @@
     <t>Exam time</t>
   </si>
   <si>
-    <t>Feel good todayS</t>
+    <t>Feel good today</t>
   </si>
 </sst>
 </file>
@@ -3360,26 +3360,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B56" s="14">
+        <v>300</v>
+      </c>
+      <c r="C56" s="14">
+        <v>20</v>
+      </c>
+      <c r="D56" s="14">
+        <v>456</v>
+      </c>
+      <c r="E56" s="14">
+        <v>45</v>
+      </c>
+      <c r="F56" s="14">
+        <v>300</v>
+      </c>
+      <c r="G56" s="14">
+        <v>5</v>
+      </c>
+      <c r="H56" s="14">
+        <v>300</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1421</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>19</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A57" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12968C3C-C029-4765-BCB7-65814F8786FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7457EF-0390-48F0-9267-E9C80177469E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Feel good today</t>
+  </si>
+  <si>
+    <t>Happy dush…</t>
   </si>
 </sst>
 </file>
@@ -3406,26 +3409,50 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="13">
+        <v>46315</v>
+      </c>
+      <c r="B57" s="14">
+        <v>320</v>
+      </c>
+      <c r="C57" s="14">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14">
+        <v>400</v>
+      </c>
+      <c r="E57" s="14">
+        <v>70</v>
+      </c>
+      <c r="F57" s="14">
+        <v>200</v>
+      </c>
+      <c r="G57" s="14">
+        <v>6</v>
+      </c>
+      <c r="H57" s="14">
+        <v>350</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1370</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>70</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A58" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7457EF-0390-48F0-9267-E9C80177469E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D0A3D7-2D11-4862-AC1D-AB67250D887E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>Happy dush…</t>
+  </si>
+  <si>
+    <t>Feel happy today</t>
   </si>
 </sst>
 </file>
@@ -3455,26 +3458,50 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="13">
+        <v>46316</v>
+      </c>
+      <c r="B58" s="14">
+        <v>300</v>
+      </c>
+      <c r="C58" s="14">
+        <v>30</v>
+      </c>
+      <c r="D58" s="14">
+        <v>420</v>
+      </c>
+      <c r="E58" s="14">
+        <v>45</v>
+      </c>
+      <c r="F58" s="14">
+        <v>300</v>
+      </c>
+      <c r="G58" s="14">
+        <v>7</v>
+      </c>
+      <c r="H58" s="14">
+        <v>300</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1395</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>45</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A59" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D0A3D7-2D11-4862-AC1D-AB67250D887E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6011DDD7-BE8E-4CD5-9CF0-D9AD335D2695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3504,26 +3504,50 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="13">
+        <v>46317</v>
+      </c>
+      <c r="B59" s="14">
+        <v>400</v>
+      </c>
+      <c r="C59" s="14">
+        <v>40</v>
+      </c>
+      <c r="D59" s="14">
+        <v>500</v>
+      </c>
+      <c r="E59" s="14">
+        <v>70</v>
+      </c>
+      <c r="F59" s="14">
+        <v>300</v>
+      </c>
+      <c r="G59" s="14">
+        <v>8</v>
+      </c>
+      <c r="H59" s="14">
+        <v>100</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1410</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>30</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A60" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6011DDD7-BE8E-4CD5-9CF0-D9AD335D2695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A61F55-E064-4A72-8C77-DB20A0F734DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Feel happy today</t>
+  </si>
+  <si>
+    <t>feeling happy today</t>
   </si>
 </sst>
 </file>
@@ -3550,26 +3553,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B60" s="14">
+        <v>399</v>
+      </c>
+      <c r="C60" s="14">
+        <v>45</v>
+      </c>
+      <c r="D60" s="14">
+        <v>340</v>
+      </c>
+      <c r="E60" s="14">
+        <v>120</v>
+      </c>
+      <c r="F60" s="14">
+        <v>239</v>
+      </c>
+      <c r="G60" s="14">
+        <v>3</v>
+      </c>
+      <c r="H60" s="14">
+        <v>123</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1266</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>174</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A61" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A61F55-E064-4A72-8C77-DB20A0F734DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4F1D9A-BBE8-4895-AC68-71C84EE110EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3599,26 +3599,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46319</v>
+      </c>
+      <c r="B61" s="14">
+        <v>400</v>
+      </c>
+      <c r="C61" s="14">
+        <v>34</v>
+      </c>
+      <c r="D61" s="14">
+        <v>453</v>
+      </c>
+      <c r="E61" s="14">
+        <v>43</v>
+      </c>
+      <c r="F61" s="14">
+        <v>34</v>
+      </c>
+      <c r="G61" s="14">
+        <v>4</v>
+      </c>
+      <c r="H61" s="14">
+        <v>432</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1396</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>44</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A62" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4F1D9A-BBE8-4895-AC68-71C84EE110EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A57B8F-3AA4-467C-8601-3A1B2F2B2607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3645,26 +3645,50 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="13">
+        <v>46320</v>
+      </c>
+      <c r="B62" s="14">
+        <v>450</v>
+      </c>
+      <c r="C62" s="14">
+        <v>50</v>
+      </c>
+      <c r="D62" s="14">
+        <v>300</v>
+      </c>
+      <c r="E62" s="14">
+        <v>50</v>
+      </c>
+      <c r="F62" s="14">
+        <v>400</v>
+      </c>
+      <c r="G62" s="14">
+        <v>7</v>
+      </c>
+      <c r="H62" s="14">
+        <v>100</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1350</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>90</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A63" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0A57B8F-3AA4-467C-8601-3A1B2F2B2607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86ECBEE-A48E-462D-9881-BAD89A1080B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>feeling happy today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feel Happy </t>
   </si>
 </sst>
 </file>
@@ -3691,26 +3694,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B63" s="14">
+        <v>400</v>
+      </c>
+      <c r="C63" s="14">
+        <v>60</v>
+      </c>
+      <c r="D63" s="14">
+        <v>340</v>
+      </c>
+      <c r="E63" s="14">
+        <v>49</v>
+      </c>
+      <c r="F63" s="14">
+        <v>400</v>
+      </c>
+      <c r="G63" s="14">
+        <v>5</v>
+      </c>
+      <c r="H63" s="14">
+        <v>190</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1439</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>1</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A64" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86ECBEE-A48E-462D-9881-BAD89A1080B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24479810-B734-4C27-9FF7-FD8A31E630BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t xml:space="preserve">Feel Happy </t>
+  </si>
+  <si>
+    <t>Feel tired &amp; sick</t>
   </si>
 </sst>
 </file>
@@ -3740,26 +3743,50 @@
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A64" s="13"/>
-      <c r="B64" s="14"/>
-      <c r="C64" s="14"/>
-      <c r="D64" s="14"/>
-      <c r="E64" s="14"/>
-      <c r="F64" s="14"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="15" t="str">
+      <c r="A64" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B64" s="14">
+        <v>350</v>
+      </c>
+      <c r="C64" s="14">
+        <v>0</v>
+      </c>
+      <c r="D64" s="14">
+        <v>280</v>
+      </c>
+      <c r="E64" s="14">
+        <v>10</v>
+      </c>
+      <c r="F64" s="14">
+        <v>230</v>
+      </c>
+      <c r="G64" s="14">
+        <v>9</v>
+      </c>
+      <c r="H64" s="14">
+        <v>100</v>
+      </c>
+      <c r="I64" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="15" t="str">
+        <v>970</v>
+      </c>
+      <c r="J64" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="17"/>
+        <v>470</v>
+      </c>
+      <c r="K64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L64" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M64" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N64" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A65" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24479810-B734-4C27-9FF7-FD8A31E630BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739C6962-C00C-4441-9D48-0824BD1CE66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3789,26 +3789,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A65" s="13"/>
-      <c r="B65" s="14"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="15" t="str">
+      <c r="A65" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B65" s="14">
+        <v>300</v>
+      </c>
+      <c r="C65" s="14">
+        <v>10</v>
+      </c>
+      <c r="D65" s="14">
+        <v>300</v>
+      </c>
+      <c r="E65" s="14">
+        <v>34</v>
+      </c>
+      <c r="F65" s="14">
+        <v>340</v>
+      </c>
+      <c r="G65" s="14">
+        <v>7</v>
+      </c>
+      <c r="H65" s="14">
+        <v>200</v>
+      </c>
+      <c r="I65" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="15" t="str">
+        <v>1184</v>
+      </c>
+      <c r="J65" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="16"/>
-      <c r="L65" s="16"/>
-      <c r="M65" s="16"/>
-      <c r="N65" s="17"/>
+        <v>256</v>
+      </c>
+      <c r="K65" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L65" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M65" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A66" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739C6962-C00C-4441-9D48-0824BD1CE66F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7AB625-1A11-4DA2-9A3E-6A035730F8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3835,26 +3835,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A66" s="13"/>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="15" t="str">
+      <c r="A66" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B66" s="14">
+        <v>400</v>
+      </c>
+      <c r="C66" s="14">
+        <v>20</v>
+      </c>
+      <c r="D66" s="14">
+        <v>400</v>
+      </c>
+      <c r="E66" s="14">
+        <v>29</v>
+      </c>
+      <c r="F66" s="14">
+        <v>400</v>
+      </c>
+      <c r="G66" s="14">
+        <v>3</v>
+      </c>
+      <c r="H66" s="14">
+        <v>35</v>
+      </c>
+      <c r="I66" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="15" t="str">
+        <v>1284</v>
+      </c>
+      <c r="J66" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
-      <c r="N66" s="17"/>
+        <v>156</v>
+      </c>
+      <c r="K66" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L66" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M66" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N66" s="17" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A67" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C7AB625-1A11-4DA2-9A3E-6A035730F8B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06A5259-F82D-499E-8D74-C5E1DF7A713D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -296,6 +296,9 @@
   </si>
   <si>
     <t>Feel tired &amp; sick</t>
+  </si>
+  <si>
+    <t>Feel bore today</t>
   </si>
 </sst>
 </file>
@@ -3881,26 +3884,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A67" s="13"/>
-      <c r="B67" s="14"/>
-      <c r="C67" s="14"/>
-      <c r="D67" s="14"/>
-      <c r="E67" s="14"/>
-      <c r="F67" s="14"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="15" t="str">
+      <c r="A67" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B67" s="14">
+        <v>450</v>
+      </c>
+      <c r="C67" s="14">
+        <v>30</v>
+      </c>
+      <c r="D67" s="14">
+        <v>340</v>
+      </c>
+      <c r="E67" s="14">
+        <v>47</v>
+      </c>
+      <c r="F67" s="14">
+        <v>340</v>
+      </c>
+      <c r="G67" s="14">
+        <v>8</v>
+      </c>
+      <c r="H67" s="14">
+        <v>199</v>
+      </c>
+      <c r="I67" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="15" t="str">
+        <v>1406</v>
+      </c>
+      <c r="J67" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="16"/>
-      <c r="L67" s="16"/>
-      <c r="M67" s="16"/>
-      <c r="N67" s="17"/>
+        <v>34</v>
+      </c>
+      <c r="K67" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L67" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N67" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A68" s="13"/>

--- a/12625759.xlsx
+++ b/12625759.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CAP776\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06A5259-F82D-499E-8D74-C5E1DF7A713D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4640956-20AC-4F1F-BD1A-D1DC0A36B914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>Feel bore today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest today </t>
   </si>
 </sst>
 </file>
@@ -3930,26 +3933,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A68" s="13"/>
-      <c r="B68" s="14"/>
-      <c r="C68" s="14"/>
-      <c r="D68" s="14"/>
-      <c r="E68" s="14"/>
-      <c r="F68" s="14"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="15" t="str">
+      <c r="A68" s="13">
+        <v>46326</v>
+      </c>
+      <c r="B68" s="14">
+        <v>450</v>
+      </c>
+      <c r="C68" s="14">
+        <v>30</v>
+      </c>
+      <c r="D68" s="14">
+        <v>350</v>
+      </c>
+      <c r="E68" s="14">
+        <v>100</v>
+      </c>
+      <c r="F68" s="14">
+        <v>200</v>
+      </c>
+      <c r="G68" s="14">
+        <v>5</v>
+      </c>
+      <c r="H68" s="14">
+        <v>200</v>
+      </c>
+      <c r="I68" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="15" t="str">
+        <v>1330</v>
+      </c>
+      <c r="J68" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="16"/>
-      <c r="L68" s="16"/>
-      <c r="M68" s="16"/>
-      <c r="N68" s="17"/>
+        <v>110</v>
+      </c>
+      <c r="K68" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="L68" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M68" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N68" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A69" s="13"/>
